--- a/AAII_Financials/Quarterly/BCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="92">
   <si>
     <t>BCS</t>
   </si>
@@ -656,265 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10305200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9692300</v>
+      </c>
+      <c r="F8" s="3">
         <v>8747000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>8784300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9204000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>9129300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>7132200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>8273700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>7506900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8133600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6427400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>7108300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7514200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8304900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>15696500</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>9096600</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>7554400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>6295300</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>6452700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>8391200</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>6531200</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>6341400</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>6186600</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>5659900</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>6191600</v>
       </c>
-      <c r="AK8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="3">
         <v>6649400</v>
       </c>
-      <c r="AM8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP8" s="3">
         <v>7004000</v>
       </c>
-      <c r="AO8" s="3" t="s">
+      <c r="AQ8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1032,53 +1044,59 @@
       <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10305200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9692300</v>
+      </c>
+      <c r="F10" s="3">
         <v>8747000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>8784300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>9204000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>9129300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>7132200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>8273700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>7506900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>8133600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>6427400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7108300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>7514200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8304900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1151,8 +1169,14 @@
       <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1218,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1339,14 @@
       <c r="AO12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,53 +1464,59 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>137300</v>
+      </c>
+      <c r="F14" s="3">
         <v>362000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>220400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>228800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>14200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-207800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-143400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>188300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>72000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1044500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-98800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>144900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-1200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1551,127 +1589,139 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>572500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>139300</v>
+      </c>
+      <c r="F15" s="3">
         <v>142000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>143800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>606200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>138200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>134000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>170200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>532700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>160400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>161800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>158900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>573100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>161100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-1128500</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-1100400</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-1065800</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-992200</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-932100</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-979000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-1033800</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-1001100</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-842700</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-793800</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-770800</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-743500</v>
       </c>
-      <c r="AM15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP15" s="3">
         <v>-815100</v>
       </c>
-      <c r="AO15" s="3" t="s">
+      <c r="AQ15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1760,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5879000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5839100</v>
+      </c>
+      <c r="F17" s="3">
         <v>5971700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5759900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5584300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5602100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5306900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5404100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4889600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5185800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5231300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4909300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4871000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5092000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>9227400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>487500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3475900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>174900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2382500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>148900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>779900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>64400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2555100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>290300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4378800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1783700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1369200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>652400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1303200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>596500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1184700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>312800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>738200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>372300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1672100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>924800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1374700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>693900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1898800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>1038900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4426200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3853100</v>
+      </c>
+      <c r="F18" s="3">
         <v>2775200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3024400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3619700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3527200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1825300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2869600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2617300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2947800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1196100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2199000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2643300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3212800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>6469100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>5620600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>5171900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>5515400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>3897700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>4012500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5161900</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5038200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>5001800</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>4921700</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>4519400</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="3">
         <v>5274600</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP18" s="3">
         <v>5105200</v>
       </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AQ18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,199 +2055,207 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
         <v>-88800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>12100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-12300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>-46300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>21400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-20200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>11500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2166400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-860700</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-999900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>330300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1776700</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2354300</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-3330400</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-899400</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-2578200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-2777000</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-2954300</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-2221200</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP20" s="3">
         <v>-3568500</v>
       </c>
-      <c r="AO20" s="3" t="s">
+      <c r="AQ20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5030500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3992400</v>
+      </c>
+      <c r="F21" s="3">
         <v>3006100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3156200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>4238300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3665400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2005600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3018400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>3170200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3108200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1346400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2360400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3213800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3374000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>5431200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>5237800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>3053100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2193,44 +2265,50 @@
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5139900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>2455300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>2938600</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>1592600</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="3">
         <v>3796800</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="3">
         <v>1636800</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2270,11 +2348,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2348,246 +2426,264 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4314700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3715800</v>
+      </c>
+      <c r="F23" s="3">
         <v>2502000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2791900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3403200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3513000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2079400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2991600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2449200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2875800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>140100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2300300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2495800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3214100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>4302700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2519600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>4759900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2771500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>4172000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2312900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5845700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2809900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2120900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1399200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1658200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1215300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1831600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>348100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>4138800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>1974500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2423600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1799400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>2144800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-305100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>1565200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>1443900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>3053400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>2214800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>1536700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>1102200</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>969900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>842500</v>
+      </c>
+      <c r="F24" s="3">
         <v>522200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>490600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>756300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>802300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>560900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>552200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>539600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>587300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-29300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>418600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>448600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>694000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>283400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>318600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1049400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>761700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>501900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>362300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>884800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>581000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>580800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>400100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>147300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>94500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>624600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>380700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>748400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>330200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>352700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>236500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>832600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>393000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>520400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>422600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>1014800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>622800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>366100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>431900</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2801,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3344800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2873300</v>
+      </c>
+      <c r="F26" s="3">
         <v>1979800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2301300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2646900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2710600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1518600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2439400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1909600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2288500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>169400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1881700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2047200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2520000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>4019300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2200900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3710500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2009800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3670100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1950500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>4960800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2229000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1540100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>999100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1510900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1120800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1207000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-32500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>3390400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1644300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>2071000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1562900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>1312200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-698100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>1044800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>1021300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>2038600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>1592000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>1170600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>670200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2997200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2551200</v>
+      </c>
+      <c r="F27" s="3">
         <v>1608300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1958500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2272900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2408300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1208100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2096200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1563300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1957600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-141400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1554700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1687600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2205800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3343500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1934800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3155900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1741800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3108700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1704900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>4474300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1995900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>983000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>745400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>906000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>805300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>530500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-413200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>2845200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1382000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1513600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1352300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>845500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-928200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>579100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>816500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>1573000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>1355000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>724200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>475400</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3176,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,17 +3265,17 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -3164,25 +3284,31 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1386500</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-3045600</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AO29" s="3">
         <v>-1054700</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AP29" s="3">
         <v>43500</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AQ29" s="3">
         <v>110600</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3426,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3551,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
         <v>88800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-12100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>12300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>46300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-21400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>20200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-11500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>2166400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>860700</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>999900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>-330300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1776700</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2354300</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>3330400</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>899400</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>2578200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>2777000</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>2954300</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN32" s="3">
         <v>2221200</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP32" s="3">
         <v>3568500</v>
       </c>
-      <c r="AO32" s="3" t="s">
+      <c r="AQ32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3319600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2873300</v>
+      </c>
+      <c r="F33" s="3">
         <v>1955600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2301300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2618200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2708000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1493500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2435300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1880500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2284700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>137600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1870700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2019300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2510100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3343500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1934800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3155900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1741800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3108700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1704900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>4474300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1995900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>983000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>745400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>906000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>805300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>530500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-413200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>2845200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>1382000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1513600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1352300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>845500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-928200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-807400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>816500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-1472600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>300200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>767700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3926,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3319600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2873300</v>
+      </c>
+      <c r="F35" s="3">
         <v>1955600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2301300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2618200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2708000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1493500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2435300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1880500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2284700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>137600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1870700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2019300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2510100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3343500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1934800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3155900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1741800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3108700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1704900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>4474300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1995900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>983000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>745400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>906000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>805300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>530500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-413200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>2845200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>1382000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1513600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1352300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>845500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-928200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-807400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>816500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-1472600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>300200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>767700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4230,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,291 +4275,305 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>326202700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>310773100</v>
+      </c>
+      <c r="F41" s="3">
         <v>315072700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>319127900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>309252000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>309411000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>268499100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>288246900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>307681300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>317344500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>289798500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>320699000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>321294700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>328921700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>349525500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>328949300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>377006300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>328654800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>314635100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>282457000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>258730500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>245411900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>236611900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>293963000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>253485700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>202067600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>204920400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>221702500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>217060100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>221039000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>247838300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>208001200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>207820500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>315505100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>239820900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>281260100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>240510900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>228958200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>193661600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>188127200</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>697630400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>645706800</v>
+      </c>
+      <c r="F42" s="3">
         <v>861779300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>633098100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>651231700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>581205200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>815701600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>602601500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>575838800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>567419000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>803491400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>535647900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>552472300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>489987900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1001384400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1228641900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1044108000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>956142800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>883749100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>907356100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>852258300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>850938900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>846891300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>906264900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>956136300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1077888800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>768021100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>975191900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>875940000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>806881700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>734231100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>732318000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>758031400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>636653300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>727053700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>610261900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>619488600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>625130300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>579809000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>792544300</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>294500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>301100</v>
+      </c>
+      <c r="F43" s="3">
         <v>371500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>295700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>238400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>253200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>194000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>193000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>222400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>318300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>154100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>133000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>127100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>383500</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4462,8 +4646,14 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4503,11 +4693,11 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4581,52 +4771,58 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7335200</v>
+      </c>
+      <c r="F45" s="3">
         <v>7983800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7977800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>7651700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>7414800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12336500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>4707600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>4988000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4700,53 +4896,59 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1275502200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1224803700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1364936700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1174421300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1177054400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1103395400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1250452600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1080966400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1073916600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1058699400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1241916700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1028354000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1039718600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>979652900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4819,365 +5021,389 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>491393100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>489774900</v>
+      </c>
+      <c r="F47" s="3">
         <v>202294800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>502848300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>502414000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>472277400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>192862800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>483267700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>455633300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>461207700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>177491500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>450294100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>451404900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>389991600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1209800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1172100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1161600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1225700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1266000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1234600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1081600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1074100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>923800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>903900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>938600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>983700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>983300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1076900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>1007900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>965300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>1006400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>896600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>921800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>905000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>936500</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN47" s="3">
         <v>932600</v>
       </c>
-      <c r="AM47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP47" s="3">
         <v>900700</v>
       </c>
-      <c r="AO47" s="3" t="s">
+      <c r="AQ47" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5607000</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>4948900</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>4800700</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>4500700</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>4612800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>4349900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>4419800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>4744900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3">
         <v>4567400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V48" s="3">
         <v>4505300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X48" s="3">
         <v>4270400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z48" s="3">
         <v>4774200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB48" s="3">
         <v>5525900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD48" s="3">
         <v>5748400</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="3">
         <v>5775600</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3">
         <v>3348200</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>3194500</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL48" s="3">
         <v>3354700</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN48" s="3">
         <v>3585500</v>
       </c>
-      <c r="AM48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP48" s="3">
         <v>3719900</v>
       </c>
-      <c r="AO48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11824300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11035200</v>
+      </c>
+      <c r="F49" s="3">
         <v>11149400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11096300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11215200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10659100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>10359700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>10887300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>9906900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9867600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>9927700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>10085900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>10937700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>10718500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>10811200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>10711600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>10513200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>9981900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>10215700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>10108800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>9773800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>9214600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>9401700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>9958000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>10641200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>10927000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>11072600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>11417100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>10975900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>10546000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>10530700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>9701300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>10175700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>10091700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>10237500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>10120100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>10074500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>10124800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>10173500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>9898300</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5521,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5646,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12237000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16183700</v>
+      </c>
+      <c r="F52" s="3">
         <v>11561200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>16069800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>11093300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>15141000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>10129300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>21204900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>13617300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>24230200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>12560500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>16953800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>10954200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>16377200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>15397400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>9305300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>13104200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>6415100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>10769500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5197700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>7717900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4747300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6219700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3573100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>7194500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3611300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>7361700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>4074100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>6889300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4697200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>7391100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>5265100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>6660600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>6661800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>7325000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>6310300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>6558100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>93769900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>101258500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>95205200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5896,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2295818000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2237917400</v>
+      </c>
+      <c r="F54" s="3">
         <v>2078284000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2189898400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2190300000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2058797900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1900674800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2052184700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1992536000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1991863900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1881957300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1942402300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1969366300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1904010800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1986275800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2209757200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2026427200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1856055500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1754304400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1745201300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1641290900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1615991100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1596340100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1734294000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1805624700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1922502400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1555032900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1825988600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1692898800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1589083200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1496828900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1441926500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1486178200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1476647600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1478106700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1498984800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1480804000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1585140000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>1597432200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>1743477400</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +6070,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,53 +6115,55 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>788585600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>775901400</v>
+      </c>
+      <c r="F57" s="3">
         <v>854068600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>773352700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>773441600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>742010900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>759976000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>727454800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>704502900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>697566200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>741760100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>684953500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>704865900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>687504900</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -5976,53 +6236,59 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>388463600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>360195700</v>
+      </c>
+      <c r="F58" s="3">
         <v>635955600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>339071700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>365907700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>317040300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>618195500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>334889400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>307020400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>305406800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>640143700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>327818300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>323860400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>305778700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6095,172 +6361,184 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>347043900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>341532100</v>
+      </c>
+      <c r="F59" s="3">
         <v>239145400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>296829000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>288013400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>280156100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>211224800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>268019000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>263585100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>256643300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>201115800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>240347300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>237441400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>257169200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>761100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>682000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>572500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1302600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>873200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>763100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>706000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>899600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>763000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>553800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>419800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>391300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>426900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1021700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>845900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>798800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>829500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>836300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>884300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1017400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>11935700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>1347400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>8521100</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP59" s="3">
         <v>12651700</v>
       </c>
-      <c r="AO59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1524093100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1477629200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1734904400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1409253400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1427362700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1339207200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1595003600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1330363200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1275108400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1259616300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1588515800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1253119100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1266167700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1250452800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6333,246 +6611,264 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>649547600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>642204900</v>
+      </c>
+      <c r="F61" s="3">
         <v>231300100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>661488800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>642133200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>605878600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>208302800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>604910900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>607979600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>616121900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>192780400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>587845700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>599692500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>549946800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>163111700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>168963500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>162928500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>151710500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>141463600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>134909700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>123510600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>120919200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>108988900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>145103400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>161457400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>143167800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>128912200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>150034200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>150526300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>143166800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>135836600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>123384200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>127340500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>129331400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>126700700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>134144400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>131139200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>135367300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>130777000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>123649200</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15914800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>16231200</v>
+      </c>
+      <c r="F62" s="3">
         <v>6407800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>15840000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>15835000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>16090600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6304700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>20872500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>18288300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>24734100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>8757100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>17246700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>16047600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>16180500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2393500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>7700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4768900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>45900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2859000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2525700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>17600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3087400</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
         <v>3918600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>686800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>4275500</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
         <v>2894700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>43900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>3986100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>77600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>4720000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>53000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>5085500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>464300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>13418700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>89648400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>91971200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>88115600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6986,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +7111,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7236,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2189925700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2136082600</v>
+      </c>
+      <c r="F66" s="3">
         <v>1972986500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2086606400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2085689800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1961199800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1809934000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1956176100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1901754100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1900500100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1790420100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1858231000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1882259700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1816601100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1896663100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2123979900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1937645800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1771117800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1666794800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1659962100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1561330700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1539733600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1518508800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1651565300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1716584300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1831496400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1467165300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1732312600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1600104200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1502993500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1414205500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1364127500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1407245700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1399700800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1394754800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1414662500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>1397502900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>1498842800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>1512008100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>1659296300</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7410,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7531,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7656,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7781,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7906,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>80143300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>77703200</v>
+      </c>
+      <c r="F72" s="3">
         <v>79748300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>78464700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>79114900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>74188300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>70142800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>74392200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>69306300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>69299600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>68444000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>66293700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>68676200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>66265800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>71722200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>63220400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>68945900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>65497500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>64192500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>64401200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>61196000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>57753300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>53865700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>62427200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>68846500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>70403200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>61104600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>63228500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>69976400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>59727900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>58541400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>59146400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>33521300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>36867100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>37438900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>43944800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>44573500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>47363600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>40202900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>46976500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +8156,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8281,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8406,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>105291200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>101237900</v>
+      </c>
+      <c r="F76" s="3">
         <v>104689100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>102688400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>103995100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>96745400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>89914500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>95124000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>89947800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>90530200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>90696500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>83365900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>85993300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>86227000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>89612800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>85777400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>88781400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>84937700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>87509600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>85239200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>79960200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>76257500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>77831300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>82728700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>89040400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>91006000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>87867600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>93676000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>92794700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>86089700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>82623300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>77798900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>78932500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>76946800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>83351900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>84322300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>83301100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>86297100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>85424100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>84181100</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8656,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3319600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2873300</v>
+      </c>
+      <c r="F81" s="3">
         <v>1955600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2301300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2618200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2708000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1493500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2435300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1880500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2284700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>137600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1870700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2019300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2510100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3343500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1934800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3155900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1741800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3108700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1704900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>4474300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1995900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>983000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>745400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>906000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>805300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>530500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-413200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>2845200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>1382000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1513600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1352300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>845500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-928200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-807400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>816500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-1472600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>300200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>767700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,8 +8960,10 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8607,11 +9003,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8685,8 +9081,14 @@
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9206,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9331,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9456,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9581,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,8 +9706,14 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9321,86 +9753,92 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>39669100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>61995000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>68022700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-4672300</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>4015200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>9377600</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>1815100</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL89" s="3">
         <v>33613400</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN89" s="3">
         <v>45704300</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP89" s="3">
         <v>-8644700</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,8 +9880,10 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9483,11 +9923,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9561,8 +10001,14 @@
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +10126,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,8 +10251,14 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9840,86 +10298,92 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>-28439300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>5411400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-21737000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>5794700</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-23447200</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>10578200</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-9478900</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL94" s="3">
         <v>1903000</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN94" s="3">
         <v>2664700</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP94" s="3">
         <v>29405200</v>
       </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,8 +10425,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10002,11 +10468,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10080,8 +10546,14 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10671,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10796,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,8 +10921,14 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10478,86 +10968,92 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>913300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>135600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>3231700</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1772900</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-837600</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-3284800</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-5559100</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL100" s="3">
         <v>879100</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN100" s="3">
         <v>374300</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP100" s="3">
         <v>516200</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,86 +11093,92 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
         <v>13555000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>-5363200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1973100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-5453800</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3">
         <v>895300</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH101" s="3">
         <v>4962200</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>521000</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-4801200</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-1424300</v>
       </c>
-      <c r="AM101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP101" s="3">
         <v>4708800</v>
       </c>
-      <c r="AO101" s="3" t="s">
+      <c r="AQ101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10716,82 +11218,88 @@
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>25698100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>62178800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>51490500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-17749700</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-19374300</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>21633200</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-12701900</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3">
         <v>31594300</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="3">
         <v>47319100</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP102" s="3">
         <v>25985500</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
